--- a/checklist_forms/039_electronic_device_production_inspection_form--checklist_forms.xlsx
+++ b/checklist_forms/039_electronic_device_production_inspection_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'passed',_'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Passed', 'value': 'passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Failed', 'value': 'failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'passed',_'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Passed', 'value': 'passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Failed', 'value': 'failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'material',_'value':_'material'}</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Material', 'value': 'material'}</t>
+          <t>Material</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'equipment',_'value':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Equipment', 'value': 'equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'labor',_'value':_'labor'}</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Labor', 'value': 'labor'}</t>
+          <t>Labor</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Defective', 'value': 'defective'}</t>
+          <t>Defective</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'non-defective',_'value':_'non_defective'}</t>
+          <t>non-defective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Defective', 'value': 'non_defective'}</t>
+          <t>Non-Defective</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'cosmetic',_'value':_'cosmetic'}</t>
+          <t>cosmetic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Cosmetic', 'value': 'cosmetic'}</t>
+          <t>Cosmetic</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'human_error',_'value':_'human_error'}</t>
+          <t>human_error</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Human Error', 'value': 'human_error'}</t>
+          <t>Human Error</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'equipment_failure',_'value':_'equipment_failure'}</t>
+          <t>equipment_failure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Equipment Failure', 'value': 'equipment_failure'}</t>
+          <t>Equipment Failure</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'material_defect',_'value':_'material_defect'}</t>
+          <t>material_defect</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Material Defect', 'value': 'material_defect'}</t>
+          <t>Material Defect</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'repair',_'value':_'repair'}</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Repair', 'value': 'repair'}</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'replace',_'value':_'replace'}</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Replace', 'value': 'replace'}</t>
+          <t>Replace</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'re-process',_'value':_'reprocess'}</t>
+          <t>re-process</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Re-process', 'value': 'reprocess'}</t>
+          <t>Re-process</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
